--- a/data/trans_camb/P19C06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,2</t>
+          <t>-1,33; 3,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,09</t>
+          <t>-0,65; 4,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,72</t>
+          <t>-1,03; 6,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,35</t>
+          <t>0,81; 6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,76</t>
+          <t>-0,83; 2,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,91</t>
+          <t>-1,93; 0,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,75</t>
+          <t>0,45; 3,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,04</t>
+          <t>-0,19; 2,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,19</t>
+          <t>-0,63; 3,2</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,54; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,77; —</t>
+          <t>-72,39; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1588,72</t>
+          <t>-9,14; 1198,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,2; —</t>
+          <t>-44,38; 864,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,78; —</t>
+          <t>-74,01; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,83</t>
+          <t>-2,23; 0,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,52</t>
+          <t>-3,15; -0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,2</t>
+          <t>-2,72; 0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,61</t>
+          <t>-2,2; 0,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; -0,13</t>
+          <t>-2,68; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,63</t>
+          <t>-2,01; 0,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,24</t>
+          <t>-1,67; 0,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; -0,59</t>
+          <t>-2,29; -0,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,1</t>
+          <t>-1,74; 0,1</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 257,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,5</t>
+          <t>-100,0; 213,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,32</t>
+          <t>-100,0; 158,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 148,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,93; 188,21</t>
+          <t>-86,42; 106,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 34,93</t>
+          <t>-84,35; 54,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,92</t>
+          <t>-100,0; -44,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 25,61</t>
+          <t>-84,33; 22,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,24</t>
+          <t>-1,26; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,35</t>
+          <t>-2,15; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,28</t>
+          <t>-1,33; 2,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,99</t>
+          <t>0,53; 5,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,72</t>
+          <t>-1,57; 0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,95</t>
+          <t>-0,68; 1,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,4</t>
+          <t>0,14; 2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,33</t>
+          <t>-1,46; 0,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,65</t>
+          <t>-0,55; 1,57</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,32; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; —</t>
+          <t>-64,8; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 1383,76</t>
+          <t>-14,28; 1059,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 710,27</t>
+          <t>-55,73; 645,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,47</t>
+          <t>-2,35; 2,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,57</t>
+          <t>-3,7; -0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,96</t>
+          <t>-2,85; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,39</t>
+          <t>-3,29; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,79</t>
+          <t>-2,56; 1,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,52</t>
+          <t>-3,17; 0,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,63</t>
+          <t>-2,41; 0,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,18</t>
+          <t>-2,36; 0,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,28</t>
+          <t>-2,39; 0,23</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,9; 274,38</t>
+          <t>-84,23; 189,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,86; 106,68</t>
+          <t>-91,66; 71,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,13; 91,52</t>
+          <t>-87,31; 94,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-87,16; 34,89</t>
+          <t>-88,87; 48,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 46,87</t>
+          <t>-84,69; 50,11</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,88</t>
+          <t>0,57; 5,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,22</t>
+          <t>-1,28; 2,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,56</t>
+          <t>-0,6; 4,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,51</t>
+          <t>-1,6; 2,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,98</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,26</t>
+          <t>-0,27; 2,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,4</t>
+          <t>-0,6; 1,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,43</t>
+          <t>-0,96; 2,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,15</t>
+          <t>-0,19; 4,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,49</t>
+          <t>-0,34; 3,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,0</t>
+          <t>-0,68; 2,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,85</t>
+          <t>-2,03; 0,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,86</t>
+          <t>-0,99; 2,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,06</t>
+          <t>-0,21; 2,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,11</t>
+          <t>-0,51; 1,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,11</t>
+          <t>-0,22; 2,14</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,61; —</t>
+          <t>-51,28; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,77; —</t>
+          <t>-61,63; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,45</t>
+          <t>-1,61; 0,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,72</t>
+          <t>-1,1; 1,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,01</t>
+          <t>-1,3; 1,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,07</t>
+          <t>-1,94; 1,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,84</t>
+          <t>-1,71; 1,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,43</t>
+          <t>-1,98; 1,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,53</t>
+          <t>-1,38; 0,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,24</t>
+          <t>-0,98; 1,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,05</t>
+          <t>-1,03; 0,93</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 698,93</t>
+          <t>-89,07; 593,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,04; 370,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 111,12</t>
+          <t>-71,11; 112,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 191,55</t>
+          <t>-65,79; 178,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 124,19</t>
+          <t>-63,94; 133,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 76,77</t>
+          <t>-68,07; 62,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 129,96</t>
+          <t>-55,09; 135,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 112,35</t>
+          <t>-52,04; 96,94</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,38</t>
+          <t>-2,3; 0,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,41</t>
+          <t>-0,84; 2,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,19</t>
+          <t>-2,56; -0,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,9</t>
+          <t>-1,01; 0,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,96</t>
+          <t>0,42; 3,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,52</t>
+          <t>-1,13; 0,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,36</t>
+          <t>-1,17; 0,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,18</t>
+          <t>0,1; 2,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,44; -0,03</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-88,78; 91,38</t>
+          <t>-91,39; 61,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 314,22</t>
+          <t>-42,7; 298,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,97</t>
+          <t>-100,0; -6,69</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,78; 501,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1220,05</t>
+          <t>8,97; 1352,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 281,33</t>
+          <t>-90,01; 313,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 63,77</t>
+          <t>-79,26; 57,17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>5,9; 325,53</t>
+          <t>3,06; 365,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-88,45; 13,95</t>
+          <t>-89,49; 7,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,44</t>
+          <t>-0,66; 0,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,72</t>
+          <t>-0,53; 0,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,3</t>
+          <t>-0,84; 0,3</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,91</t>
+          <t>-0,27; 0,91</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,74</t>
+          <t>-0,37; 0,78</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,38</t>
+          <t>-0,6; 0,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,45</t>
+          <t>-0,31; 0,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,55</t>
+          <t>-0,27; 0,58</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,27</t>
+          <t>-0,54; 0,21</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 54,42</t>
+          <t>-47,05; 65,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 92,43</t>
+          <t>-39,19; 82,75</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 42,57</t>
+          <t>-58,94; 44,67</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 108,3</t>
+          <t>-20,29; 107,56</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 86,53</t>
+          <t>-26,25; 91,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 43,48</t>
+          <t>-41,72; 53,12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 48,82</t>
+          <t>-23,62; 54,46</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 59,02</t>
+          <t>-20,43; 64,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 31,47</t>
+          <t>-42,23; 22,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,1</t>
+          <t>-1,52; 2,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,7</t>
+          <t>-0,73; 4,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 6,81</t>
+          <t>-1,27; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,35</t>
+          <t>0,98; 6,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,93</t>
+          <t>-1,17; 2,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,91</t>
+          <t>-2,0; 0,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,83</t>
+          <t>0,49; 4,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,92</t>
+          <t>-0,2; 3,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,2</t>
+          <t>-0,94; 1,5</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>-8,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-88,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,39; —</t>
+          <t>-75,83; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 1198,12</t>
+          <t>-6,51; 1522,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 864,95</t>
+          <t>-44,37; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,01; —</t>
+          <t>-80,42; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,73</t>
+          <t>-2,29; 0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,72</t>
+          <t>-3,25; -0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,05</t>
+          <t>-2,57; 0,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,51</t>
+          <t>-2,05; 0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,13</t>
+          <t>-2,38; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,56</t>
+          <t>-1,88; 0,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,36</t>
+          <t>-1,66; 0,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -0,57</t>
+          <t>-2,36; -0,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,1</t>
+          <t>-1,74; 0,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-69,31%</t>
+          <t>-69,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,88%</t>
+          <t>-41,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-54,91%</t>
+          <t>-56,29%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 159,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,45</t>
+          <t>-100,0; 151,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,05</t>
+          <t>-100,0; 118,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,06</t>
+          <t>-100,0; 144,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 106,9</t>
+          <t>-84,3; 153,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 54,83</t>
+          <t>-82,9; 55,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -44,49</t>
+          <t>-100,0; -15,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-84,33; 22,13</t>
+          <t>-84,76; 23,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,02</t>
+          <t>-1,25; 2,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,31</t>
+          <t>-2,39; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,25</t>
+          <t>-1,39; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,27</t>
+          <t>0,48; 5,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,73</t>
+          <t>-1,57; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,94</t>
+          <t>-0,72; 1,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,99</t>
+          <t>0,15; 3,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,3</t>
+          <t>-1,49; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,57</t>
+          <t>-0,46; 1,62</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>109,12%</t>
+          <t>110,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,12; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,8; —</t>
+          <t>-66,78; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 1059,7</t>
+          <t>-18,04; 1030,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 645,7</t>
+          <t>-49,02; 660,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,1</t>
+          <t>-2,57; 1,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,34</t>
+          <t>-3,95; -0,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,97</t>
+          <t>-2,97; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,42</t>
+          <t>-3,28; 0,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,58</t>
+          <t>-2,57; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,4</t>
+          <t>-3,18; 0,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,65</t>
+          <t>-2,18; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,28</t>
+          <t>-2,33; 0,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,23</t>
+          <t>-2,24; 0,32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,1%</t>
+          <t>-48,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-55,87%</t>
+          <t>-45,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,66%</t>
+          <t>-46,6%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,23; 189,18</t>
+          <t>-81,21; 191,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,66; 71,12</t>
+          <t>-91,62; 123,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,31; 94,07</t>
+          <t>-85,05; 90,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,87; 48,0</t>
+          <t>-87,36; 48,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,69; 50,11</t>
+          <t>-83,63; 45,99</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,04</t>
+          <t>0,58; 4,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1556,32 +1556,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,05</t>
+          <t>-1,39; 1,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,06</t>
+          <t>-1,17; 3,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,59</t>
+          <t>-2,39; 0,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>-0,04; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,39</t>
+          <t>-0,28; 2,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,37</t>
+          <t>-1,43; 0,21</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>-66,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>-64,34%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,34</t>
+          <t>-1,01; 2,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,25</t>
+          <t>-0,17; 4,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,29</t>
+          <t>-0,45; 3,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,86</t>
+          <t>-0,78; 2,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,84</t>
+          <t>-1,62; 0,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,03</t>
+          <t>-0,96; 1,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,18</t>
+          <t>-0,31; 2,05</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,86</t>
+          <t>-0,46; 2,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,14</t>
+          <t>-0,24; 2,03</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>247,71%</t>
+          <t>236,93%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>129,06%</t>
+          <t>122,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>187,53%</t>
+          <t>177,71%</t>
         </is>
       </c>
     </row>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,28; —</t>
+          <t>-65,62; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-61,63; —</t>
+          <t>-57,52; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,45</t>
+          <t>-1,63; 0,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,87</t>
+          <t>-1,03; 2,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,01</t>
+          <t>-1,48; 0,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,2</t>
+          <t>-1,85; 1,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,78</t>
+          <t>-1,72; 1,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,46</t>
+          <t>-0,95; 2,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,53</t>
+          <t>-1,51; 0,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,28</t>
+          <t>-1,01; 1,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,93</t>
+          <t>-0,96; 1,02</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,45%</t>
+          <t>-17,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 238,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,07; 593,72</t>
+          <t>-80,23; 1021,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 370,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 112,31</t>
+          <t>-71,0; 128,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 178,54</t>
+          <t>-68,16; 170,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 133,96</t>
+          <t>-34,86; 188,71</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 62,26</t>
+          <t>-71,12; 62,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 135,06</t>
+          <t>-54,48; 154,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 96,94</t>
+          <t>-46,23; 116,54</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,32</t>
+          <t>-2,1; 0,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,4</t>
+          <t>-0,76; 2,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,19</t>
+          <t>-2,34; -0,09</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,92</t>
+          <t>-0,91; 0,81</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,02</t>
+          <t>0,38; 2,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,45</t>
+          <t>-1,25; 0,43</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,32</t>
+          <t>-1,13; 0,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,2</t>
+          <t>0,14; 2,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,03</t>
+          <t>-1,33; 0,06</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-76,71%</t>
+          <t>-69,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-33,35%</t>
+          <t>-35,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-62,82%</t>
+          <t>-57,96%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-91,39; 61,66</t>
+          <t>-91,46; 84,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 298,24</t>
+          <t>-41,2; 324,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,69</t>
+          <t>-100,0; 18,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 501,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,97; 1352,68</t>
+          <t>11,08; 1443,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 313,83</t>
+          <t>-91,81; 267,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-79,26; 57,17</t>
+          <t>-76,29; 68,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,06; 365,63</t>
+          <t>5,28; 335,89</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-89,49; 7,37</t>
+          <t>-85,76; 22,01</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,47</t>
+          <t>-0,69; 0,45</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,68</t>
+          <t>-0,52; 0,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,3</t>
+          <t>-0,85; 0,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,91</t>
+          <t>-0,29; 0,86</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,78</t>
+          <t>-0,37; 0,83</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,44</t>
+          <t>-0,55; 0,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,51</t>
+          <t>-0,32; 0,5</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,58</t>
+          <t>-0,27; 0,57</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,21</t>
+          <t>-0,54; 0,18</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-24,4%</t>
+          <t>-29,98%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-3,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-15,94%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 65,45</t>
+          <t>-49,15; 57,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 82,75</t>
+          <t>-39,22; 80,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 44,67</t>
+          <t>-61,84; 27,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 107,56</t>
+          <t>-22,06; 101,26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 91,49</t>
+          <t>-26,75; 100,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 53,12</t>
+          <t>-38,07; 54,35</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 54,46</t>
+          <t>-25,54; 55,42</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 64,77</t>
+          <t>-20,3; 63,09</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 22,38</t>
+          <t>-39,84; 20,75</t>
         </is>
       </c>
     </row>
